--- a/outreach/melbourne-airbnb/Melbourne_Airbnb_call_list.xlsx
+++ b/outreach/melbourne-airbnb/Melbourne_Airbnb_call_list.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Call list" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Excluded" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Real estate agents" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Call list'!$A$1:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Real estate agents'!$A$1:$O$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +40,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +62,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B3F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF0E4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -84,6 +96,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1324,8 +1341,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Hawthorn</t>
@@ -1362,7 +1377,6 @@
           <t>only 1 reviews - unproven</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1432,8 +1446,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Ascot Vale</t>
@@ -1465,8 +1477,6 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1532,8 +1542,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Brighton</t>
@@ -1565,8 +1573,6 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1632,8 +1638,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Camberwell</t>
@@ -1665,8 +1669,6 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1732,8 +1734,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Glen Waverley</t>
@@ -1765,8 +1765,6 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1844,8 +1842,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Port Melbourne</t>
@@ -1877,8 +1873,6 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1944,8 +1938,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Cremorne</t>
@@ -1982,7 +1974,6 @@
           <t>only 4 reviews - unproven</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2048,8 +2039,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Elwood</t>
@@ -2081,8 +2070,6 @@
           <t>KEEP</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2156,8 +2143,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Richmond</t>
@@ -2194,7 +2179,6 @@
           <t>only 2 reviews - unproven</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2260,8 +2244,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>Brighton East</t>
@@ -2298,7 +2280,6 @@
           <t>brand-new host, no revenue history; only 2 reviews - unproven; rating 4.5 soft</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2364,8 +2345,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>Glen Iris</t>
@@ -2402,7 +2381,6 @@
           <t>$395/nt - low budget</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2472,8 +2450,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>Docklands</t>
@@ -2510,7 +2486,6 @@
           <t>only 1 reviews - unproven; $348/nt - low budget</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2580,8 +2555,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>Moonee Ponds</t>
@@ -2618,7 +2591,6 @@
           <t>$300/nt - low budget</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2682,8 +2654,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>Southbank</t>
@@ -2697,7 +2667,6 @@
       <c r="H46" t="n">
         <v>4</v>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" s="6" t="inlineStr">
         <is>
           <t>Open listing</t>
@@ -2718,7 +2687,6 @@
           <t>rating 4.65 soft</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2782,8 +2750,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>Docklands</t>
@@ -2797,7 +2763,6 @@
       <c r="H48" t="n">
         <v>4</v>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" s="6" t="inlineStr">
         <is>
           <t>Open listing</t>
@@ -2818,7 +2783,6 @@
           <t>rating 4.64 soft</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2882,8 +2846,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>Port Melbourne</t>
@@ -2897,7 +2859,6 @@
       <c r="H50" t="n">
         <v>3</v>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr">
         <is>
           <t>Open listing</t>
@@ -2918,7 +2879,6 @@
           <t>rating 4.71 soft</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2986,8 +2946,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>Alphington</t>
@@ -3001,7 +2959,6 @@
       <c r="H52" t="n">
         <v>4</v>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
           <t>Open listing</t>
@@ -3022,7 +2979,6 @@
           <t>only 1 reviews - unproven</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N52"/>
@@ -3560,4 +3516,1135 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Agent(s) - call these</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Price guide</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>What's on the listing now</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>Why closeable</t>
+        </is>
+      </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>Listing link</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>72</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kate Strickland</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0400 125 946</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Marshall White Bayside</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>126 Cochrane Street, Brighton</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Enquire (premium)</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EOI Tue 15 Sep 2pm</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Gallery(5) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>25 days of campaign left; price withheld = top-end campaign, biggest VPA; agent has 2 listings in this set - portfolio deal; only 5 photos - thin campaign</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Malvern</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Joanna Nairn; David Volpato</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>0419 994 664 / 0414 701 983</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Marshall White Stonnington</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>17 Wilks Avenue, Malvern</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>$4.0M-$4.4M</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Auction Wed 16 Sep</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Gallery(11) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>26 days of campaign left; $3M+ - large VPA budget; agent has 2 listings in this set - portfolio deal; only 11 photos - thin campaign</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>64</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Camberwell</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Andrew Gibbons; Nick Ptak; Jess Cleland</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0407 577 007 / 0413 370 442</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Marshall White Boroondara</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8 Kingsley Street, Camberwell</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>$3.6M-$3.9M</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Auction Sat 12 Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Gallery + Floorplan</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>22 days of campaign left; $3M+ - large VPA budget; agent has 2 listings in this set - portfolio deal</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Balwyn</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Scarlett Hang; Daniel Bradd</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>0405 054 888 / 0411 347 511</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Marshall White Balwyn</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>7 Relowe Crescent, Balwyn</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>$2.8M-$3.05M</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Auction Fri 18 Sep</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Gallery + Floorplan</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>28 days of campaign left; agent has 2 listings in this set - portfolio deal; 5BR - lots to film</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>62</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hawthorn East</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stuart Evans; Jess Cleland</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0402 067 710 / 0411 691 973</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Marshall White Boroondara</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>394 Tooronga Road, Hawthorn East</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>$2.5M-$2.75M</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Auction Fri 18 Sep</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Gallery(14) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>28 days of campaign left; agent has 2 listings in this set - portfolio deal; 5BR - lots to film</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Brighton East</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Kate Strickland; Spiro Vasiliadis</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>0400 125 946</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Marshall White Bayside</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>28 Sunlight Crescent, Brighton East</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>$2.4M-$2.55M</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Auction Sat 12 Sep 11:30am</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Photos(16) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>22 days of campaign left; agent has 2 listings in this set - portfolio deal</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Armadale</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Joanna Nairn; Joseph Ben-Danan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0419 994 664 / 0408 135 948</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Marshall White Stonnington</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>45 Northcote Road, Armadale</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$1.6M-$1.7M</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Auction Fri 11 Sep</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Gallery(11) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>21 days of campaign left; agent has 2 listings in this set - portfolio deal; only 11 photos - thin campaign</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Balwyn North</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>James Tostevin; Scarlett Hang</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>0417 003 333 / 0405 054 888</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Marshall White Balwyn</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>43 Yeneda Street, Balwyn North</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>$1.8M-$1.95M</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Auction Fri 11 Sep</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Gallery(11) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>21 days of campaign left; agent has 2 listings in this set - portfolio deal; only 11 photos - thin campaign</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Andy Nasr; Simon Monnier-Penny</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0422 029 324 / 0404 283 551</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Marshall White Bayside</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4 Norwood Avenue, Brighton</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>EOI (premium)</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>EOI Mon 14 Sep 1pm</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Gallery(20) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>24 days of campaign left; price withheld = top-end campaign, biggest VPA</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Glen Iris</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Daniel Wheeler; Ash Howarth</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>0411 676 058</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Marshall White Stonnington</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>77 Summerhill Road, Glen Iris</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>$3.0M-$3.3M</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Auction Sat 5 Sep 12:30pm</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Photos(18) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>15 days left - workable; $3M+ - large VPA budget; 5BR - lots to film</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>45</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Glen Iris</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cameron Edgoose; Jason Brinkworth</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0438 064 212 / 0416 006 282</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Marshall White Boroondara</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>50 Beryl Street, Glen Iris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>$2.1M-$2.3M</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Auction Fri 11 Sep</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Gallery(16) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>21 days of campaign left</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Ben Vieth; Ewan Bennett</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>0404 084 793 / 0430 958 869</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Marshall White Bayside</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>2/7 Grantham Court, Brighton</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>EOI (premium)</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>EOI Mon 7 Sep 12pm</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Gallery(23) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>17 days left - workable; price withheld = top-end campaign, biggest VPA</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>42</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kew</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Davide Lettieri; Tom Rogan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0414 018 707 / 0400 595 527</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Marshall White Boroondara</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>94 Disraeli Street, Kew</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$2.0M-$2.2M</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Private sale - no deadline</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Gallery(15) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>private sale - no deadline, open runway</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Brighton East</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Julian Augustini; Romana Preston</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>0418 558 408</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Hodges Brighton</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>5 Stradbroke Avenue, Brighton East</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>$1.55M-$1.65M</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Auction Sat 12 Sep 11:00am</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Photos(19) + Floorplan</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>22 days of campaign left</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>28</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brighton East</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Calvin Reid; Eileen Bell</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0413 878 860</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jellis Craig Brighton</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>60 Landcox Street, Brighton East</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$1.6M-$1.7M</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Auction Sat 29 Aug 1:00pm</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Photos(14) only - no floorplan</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>only 8 days left - call today or skip; 5BR - lots to film; no floorplan either</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Open listing</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O16"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId15"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>